--- a/docs/downloads/05/tbl_comfort_marovoay_bepako.xlsx
+++ b/docs/downloads/05/tbl_comfort_marovoay_bepako.xlsx
@@ -383,10 +383,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>305</v>
+        <v>621</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>504.9</v>
       </c>
     </row>
     <row r="3">
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>1282</v>
+        <v>2564</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
